--- a/education_forms/046_school_clothing_application_form--education_forms.xlsx
+++ b/education_forms/046_school_clothing_application_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parent',_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Parent', 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'guardian',_'label':_'guardian'}</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Guardian', 'label': 'Guardian'}</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'public_school',_'label':_'public_school'}</t>
+          <t>public_school</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Public School', 'label': 'Public School'}</t>
+          <t>Public School</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'private_school',_'label':_'private_school'}</t>
+          <t>private_school</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Private School', 'label': 'Private School'}</t>
+          <t>Private School</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'primary_1-5',_'label':_'primary_1-5'}</t>
+          <t>primary_1-5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Primary 1-5', 'label': 'Primary 1-5'}</t>
+          <t>Primary 1-5</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'high_school',_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'High School', 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'college',_'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'College', 'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'grade_1',_'label':_'grade_1'}</t>
+          <t>grade_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Grade 1', 'label': 'Grade 1'}</t>
+          <t>Grade 1</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'grade_2',_'label':_'grade_2'}</t>
+          <t>grade_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Grade 2', 'label': 'Grade 2'}</t>
+          <t>Grade 2</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'grade_3',_'label':_'grade_3'}</t>
+          <t>grade_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Grade 3', 'label': 'Grade 3'}</t>
+          <t>Grade 3</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'grade_4',_'label':_'grade_4'}</t>
+          <t>grade_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Grade 4', 'label': 'Grade 4'}</t>
+          <t>Grade 4</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'grade_5',_'label':_'grade_5'}</t>
+          <t>grade_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Grade 5', 'label': 'Grade 5'}</t>
+          <t>Grade 5</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'grade_6',_'label':_'grade_6'}</t>
+          <t>grade_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Grade 6', 'label': 'Grade 6'}</t>
+          <t>Grade 6</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'grade_7',_'label':_'grade_7'}</t>
+          <t>grade_7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Grade 7', 'label': 'Grade 7'}</t>
+          <t>Grade 7</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'grade_8',_'label':_'grade_8'}</t>
+          <t>grade_8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Grade 8', 'label': 'Grade 8'}</t>
+          <t>Grade 8</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'grade_9',_'label':_'grade_9'}</t>
+          <t>grade_9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Grade 9', 'label': 'Grade 9'}</t>
+          <t>Grade 9</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'grade_10',_'label':_'grade_10'}</t>
+          <t>grade_10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Grade 10', 'label': 'Grade 10'}</t>
+          <t>Grade 10</t>
         </is>
       </c>
     </row>
